--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -424,11 +424,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="6">
@@ -439,56 +439,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C6">
-        <v>108</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C7">
-        <v>144</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C8">
-        <v>180</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C10">
-        <v>216</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C11">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C13">
-        <v>34</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14">
@@ -559,11 +559,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C14">
-        <v>108</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15">
@@ -574,11 +574,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C15">
-        <v>18</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16">
@@ -589,101 +589,296 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C16">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C18">
-        <v>216</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C19">
-        <v>252</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C20">
-        <v>168</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C21">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>JA 625</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JA 625</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JA 625</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>QTI</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>JA 625</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SLA</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JA 625</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Longi 615</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Longi 620</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>TQG</t>
         </is>
       </c>
-      <c r="C22">
+      <c r="C34">
         <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -469,11 +469,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C8">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -484,41 +484,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C9">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C10">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C11">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C12">
-        <v>144</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C13">
-        <v>288</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -559,11 +559,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C14">
-        <v>216</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
@@ -574,11 +574,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C15">
-        <v>216</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -589,11 +589,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C16">
-        <v>19</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17">
@@ -604,11 +604,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C17">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C18">
-        <v>306</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C19">
-        <v>216</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C20">
-        <v>88</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C21">
-        <v>200</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C22">
-        <v>34</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C23">
-        <v>144</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C24">
-        <v>108</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C25">
-        <v>18</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26">
@@ -739,116 +739,116 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C26">
-        <v>44</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C28">
-        <v>216</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C30">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C31">
-        <v>324</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C32">
-        <v>74</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C33">
-        <v>226</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -859,11 +859,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35">
@@ -874,11 +874,131 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>TTH</t>
         </is>
       </c>
-      <c r="C35">
-        <v>36</v>
+      <c r="C43">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,16 +374,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -394,26 +394,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -424,11 +424,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C5">
-        <v>2142</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -439,11 +439,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="7">
@@ -454,11 +454,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C7">
-        <v>108</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -469,11 +469,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9">
@@ -484,11 +484,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C9">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C10">
-        <v>74</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -514,41 +514,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C13">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -559,11 +559,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C14">
-        <v>144</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -574,11 +574,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -589,11 +589,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C16">
-        <v>369</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -604,11 +604,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C17">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C18">
-        <v>19</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C19">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C20">
-        <v>252</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C21">
-        <v>306</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C22">
-        <v>252</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C23">
-        <v>30</v>
+        <v>522</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C24">
-        <v>224</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C25">
-        <v>180</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26">
@@ -739,11 +739,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C26">
-        <v>251</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27">
@@ -754,11 +754,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C27">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -769,11 +769,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C28">
-        <v>108</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29">
@@ -784,11 +784,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C29">
-        <v>18</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30">
@@ -799,11 +799,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C30">
-        <v>60</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31">
@@ -814,11 +814,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C31">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
@@ -829,56 +829,56 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C32">
-        <v>36</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C34">
-        <v>216</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -889,11 +889,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C36">
-        <v>46</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37">
@@ -904,11 +904,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C37">
-        <v>324</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -919,11 +919,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39">
@@ -934,11 +934,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -949,11 +949,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41">
@@ -964,11 +964,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C41">
-        <v>36</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42">
@@ -979,11 +979,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43">
@@ -994,11 +994,86 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>TTH</t>
         </is>
       </c>
-      <c r="C43">
-        <v>42</v>
+      <c r="C47">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,26 +379,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>2230</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="7">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
@@ -469,11 +469,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C8">
-        <v>111</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -484,11 +484,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C9">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C11">
-        <v>43</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C12">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -544,41 +544,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C13">
-        <v>74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C15">
-        <v>40</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16">
@@ -589,11 +589,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C16">
-        <v>144</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
@@ -604,11 +604,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C18">
-        <v>513</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C19">
-        <v>72</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C20">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C21">
-        <v>112</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C22">
-        <v>72</v>
+        <v>694</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C23">
-        <v>522</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C25">
-        <v>252</v>
+        <v>382</v>
       </c>
     </row>
     <row r="26">
@@ -739,11 +739,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C26">
-        <v>69</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27">
@@ -754,11 +754,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C27">
-        <v>44</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28">
@@ -769,11 +769,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C28">
-        <v>396</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -784,11 +784,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="C29">
-        <v>395</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -799,11 +799,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C30">
-        <v>139</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31">
@@ -814,11 +814,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C31">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
@@ -829,11 +829,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C32">
-        <v>269</v>
+        <v>581</v>
       </c>
     </row>
     <row r="33">
@@ -844,11 +844,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>695</v>
       </c>
     </row>
     <row r="34">
@@ -859,146 +859,146 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C34">
-        <v>36</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C36">
-        <v>216</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C37">
-        <v>20</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C38">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C40">
-        <v>74</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C41">
-        <v>324</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C42">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C43">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C45">
-        <v>82</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
@@ -1039,11 +1039,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C46">
-        <v>28</v>
+        <v>209</v>
       </c>
     </row>
     <row r="47">
@@ -1054,26 +1054,206 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C47">
-        <v>38</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C48">
-        <v>20</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NBH</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>QTI</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,46 +374,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -424,161 +424,161 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C6">
-        <v>2446</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C7">
-        <v>108</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C9">
-        <v>36</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C10">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C11">
-        <v>160</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C12">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C15">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -589,11 +589,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C16">
-        <v>202</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17">
@@ -604,11 +604,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C17">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C18">
-        <v>48</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C19">
-        <v>144</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C20">
-        <v>36</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C21">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C22">
-        <v>694</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C23">
-        <v>252</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C24">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C25">
-        <v>382</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26">
@@ -739,266 +739,266 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C26">
-        <v>288</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C27">
-        <v>336</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C28">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C29">
-        <v>36</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C30">
-        <v>343</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C31">
-        <v>107</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C32">
-        <v>581</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C33">
-        <v>695</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C34">
-        <v>329</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C35">
-        <v>202</v>
+        <v>576</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C36">
-        <v>20</v>
+        <v>540</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C37">
-        <v>108</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C38">
-        <v>54</v>
+        <v>372</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C39">
-        <v>500</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C40">
-        <v>252</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C42">
-        <v>16</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44">
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C44">
-        <v>438</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C45">
-        <v>24</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46">
@@ -1039,11 +1039,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C46">
-        <v>209</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C47">
-        <v>244</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C48">
-        <v>22</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
@@ -1084,11 +1084,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C49">
-        <v>252</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50">
@@ -1099,11 +1099,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C50">
-        <v>28</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51">
@@ -1114,11 +1114,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C51">
-        <v>324</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52">
@@ -1129,131 +1129,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C52">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NBH</t>
-        </is>
-      </c>
-      <c r="C53">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
-      <c r="C54">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>QNI</t>
-        </is>
-      </c>
-      <c r="C55">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>QTI</t>
-        </is>
-      </c>
-      <c r="C56">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>TNH</t>
-        </is>
-      </c>
-      <c r="C57">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>TQG</t>
-        </is>
-      </c>
-      <c r="C58">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>TTH</t>
-        </is>
-      </c>
-      <c r="C59">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="C60">
-        <v>108</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,16 +374,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -394,7 +394,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C3">
@@ -409,11 +409,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5">
@@ -434,31 +434,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C6">
-        <v>147</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -469,11 +469,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C8">
-        <v>176</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
@@ -484,11 +484,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C9">
-        <v>128</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C10">
-        <v>66</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="C11">
-        <v>262</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C13">
-        <v>504</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -559,11 +559,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C14">
-        <v>83</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -574,11 +574,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C15">
-        <v>58</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
@@ -589,11 +589,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C16">
-        <v>180</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -604,11 +604,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C17">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C18">
-        <v>370</v>
+        <v>468</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C19">
-        <v>74</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C20">
-        <v>1803</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C21">
-        <v>43</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C23">
-        <v>89</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C24">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C25">
-        <v>260</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
@@ -739,71 +739,71 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C26">
-        <v>1656</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C28">
-        <v>34</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C29">
-        <v>140</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C30">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -814,11 +814,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C31">
-        <v>144</v>
+        <v>772</v>
       </c>
     </row>
     <row r="32">
@@ -829,11 +829,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C32">
-        <v>62</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33">
@@ -844,11 +844,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C33">
-        <v>108</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
@@ -859,11 +859,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C34">
-        <v>16</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35">
@@ -874,11 +874,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C35">
-        <v>576</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36">
@@ -889,11 +889,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C36">
-        <v>540</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37">
@@ -904,11 +904,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C37">
-        <v>247</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -919,11 +919,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C38">
-        <v>372</v>
+        <v>576</v>
       </c>
     </row>
     <row r="39">
@@ -934,11 +934,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C39">
-        <v>36</v>
+        <v>253</v>
       </c>
     </row>
     <row r="40">
@@ -949,11 +949,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C40">
-        <v>36</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41">
@@ -964,11 +964,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C41">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42">
@@ -979,11 +979,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C42">
-        <v>451</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
@@ -994,11 +994,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C43">
-        <v>451</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C44">
-        <v>90</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C45">
-        <v>218</v>
+        <v>451</v>
       </c>
     </row>
     <row r="46">
@@ -1039,11 +1039,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C46">
-        <v>58</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C47">
-        <v>163</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C48">
-        <v>82</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49">
@@ -1084,11 +1084,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C49">
-        <v>380</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50">
@@ -1099,11 +1099,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C50">
-        <v>134</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51">
@@ -1114,11 +1114,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C51">
-        <v>275</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52">
@@ -1129,11 +1129,56 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C52">
-        <v>288</v>
+      <c r="C55">
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,16 +374,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -394,11 +394,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -409,11 +409,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C4">
-        <v>252</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -424,11 +424,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C5">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -439,11 +439,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C6">
-        <v>720</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -454,26 +454,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C7">
-        <v>504</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C8">
-        <v>147</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9">
@@ -484,11 +484,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C10">
-        <v>145</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C11">
-        <v>2160</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="C12">
-        <v>108</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C13">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -559,11 +559,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C14">
-        <v>128</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -574,11 +574,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C15">
-        <v>93</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -589,11 +589,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C16">
-        <v>270</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -604,11 +604,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C17">
-        <v>28</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C18">
-        <v>468</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C19">
-        <v>130</v>
+        <v>540</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C20">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C21">
-        <v>291</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C22">
-        <v>86</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C23">
-        <v>1687</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C24">
-        <v>43</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C25">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -739,11 +739,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C26">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
@@ -754,11 +754,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C27">
-        <v>14</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
@@ -769,11 +769,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C28">
-        <v>260</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -784,56 +784,56 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C29">
-        <v>1684</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C31">
-        <v>772</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C32">
-        <v>140</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -844,11 +844,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C33">
-        <v>30</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
@@ -859,11 +859,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C34">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35">
@@ -874,11 +874,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C35">
-        <v>159</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36">
@@ -889,11 +889,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C36">
-        <v>108</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37">
@@ -904,11 +904,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C37">
-        <v>16</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38">
@@ -919,11 +919,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C38">
-        <v>576</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -934,11 +934,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C39">
-        <v>253</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40">
@@ -949,11 +949,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C40">
-        <v>144</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41">
@@ -964,11 +964,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C41">
-        <v>185</v>
+        <v>469</v>
       </c>
     </row>
     <row r="42">
@@ -979,11 +979,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C42">
-        <v>32</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43">
@@ -994,11 +994,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C43">
-        <v>36</v>
+        <v>329</v>
       </c>
     </row>
     <row r="44">
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C44">
-        <v>184</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C45">
-        <v>451</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46">
@@ -1039,11 +1039,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C46">
-        <v>379</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C47">
-        <v>108</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C48">
-        <v>218</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49">
@@ -1084,11 +1084,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C49">
-        <v>58</v>
+        <v>451</v>
       </c>
     </row>
     <row r="50">
@@ -1099,11 +1099,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C50">
-        <v>265</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51">
@@ -1114,11 +1114,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C51">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C52">
-        <v>1100</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53">
@@ -1144,11 +1144,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C53">
-        <v>160</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
@@ -1159,11 +1159,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C54">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55">
@@ -1174,11 +1174,71 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C55">
         <v>294</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,16 +374,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -394,11 +394,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -409,11 +409,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -424,56 +424,56 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C5">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C7">
-        <v>720</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C8">
-        <v>504</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -484,11 +484,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C9">
-        <v>147</v>
+        <v>615</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C11">
-        <v>129</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C12">
-        <v>2160</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C13">
-        <v>108</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -559,11 +559,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C14">
-        <v>28</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -574,266 +574,266 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C16">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C17">
-        <v>197</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C18">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C19">
-        <v>540</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C20">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C21">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C22">
-        <v>365</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C23">
-        <v>86</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C24">
-        <v>379</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C25">
-        <v>43</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C26">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C27">
-        <v>86</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C28">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C29">
-        <v>106</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C30">
-        <v>91</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C31">
-        <v>1684</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -844,11 +844,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C33">
-        <v>110</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34">
@@ -859,11 +859,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C34">
-        <v>140</v>
+        <v>769</v>
       </c>
     </row>
     <row r="35">
@@ -874,11 +874,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C35">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -889,11 +889,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C36">
-        <v>157</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -904,11 +904,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C37">
-        <v>110</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -919,11 +919,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C38">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -934,11 +934,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C39">
-        <v>108</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40">
@@ -949,11 +949,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C40">
-        <v>288</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41">
@@ -964,11 +964,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C41">
-        <v>469</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
@@ -979,11 +979,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C42">
-        <v>144</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43">
@@ -994,251 +994,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C43">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>HTH</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>HYN</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>LDG</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LSN</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NBH</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
-      <c r="C50">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C51">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>QTI</t>
-        </is>
-      </c>
-      <c r="C52">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SLA</t>
-        </is>
-      </c>
-      <c r="C53">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="C54">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>TNH</t>
-        </is>
-      </c>
-      <c r="C55">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>TNN</t>
-        </is>
-      </c>
-      <c r="C56">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>TQG</t>
-        </is>
-      </c>
-      <c r="C57">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>TTH</t>
-        </is>
-      </c>
-      <c r="C58">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="C59">
-        <v>288</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,7 +398,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>98</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -454,11 +454,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>615</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C10">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C11">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C12">
-        <v>29</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C13">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -569,22 +569,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -593,22 +593,22 @@
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C19">
-        <v>68</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C20">
-        <v>130</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -664,7 +664,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C21">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C23">
-        <v>36</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C24">
-        <v>144</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C25">
-        <v>324</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26">
@@ -739,11 +739,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C26">
-        <v>68</v>
+        <v>720</v>
       </c>
     </row>
     <row r="27">
@@ -754,11 +754,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C27">
-        <v>252</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -769,11 +769,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C28">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
@@ -784,11 +784,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C29">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
@@ -799,11 +799,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -814,11 +814,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C31">
-        <v>36</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32">
@@ -829,11 +829,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C32">
-        <v>18</v>
+        <v>759</v>
       </c>
     </row>
     <row r="33">
@@ -844,11 +844,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C33">
-        <v>132</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34">
@@ -859,11 +859,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C34">
-        <v>769</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
@@ -874,11 +874,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C35">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -889,11 +889,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
@@ -904,11 +904,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C37">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38">
@@ -919,11 +919,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39">
@@ -934,11 +934,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C39">
-        <v>153</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40">
@@ -949,11 +949,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C40">
-        <v>312</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41">
@@ -964,11 +964,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C41">
-        <v>52</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42">
@@ -979,26 +979,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C42">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>472</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,7 +398,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>106</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>474</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C11">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C12">
-        <v>72</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C13">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -589,7 +589,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C16">
@@ -599,16 +599,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C17">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C18">
-        <v>36</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C19">
-        <v>130</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C20">
-        <v>32</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C21">
-        <v>32</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C22">
-        <v>108</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C23">
-        <v>288</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C24">
-        <v>68</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C25">
-        <v>252</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26">
@@ -739,11 +739,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C26">
-        <v>720</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27">
@@ -754,11 +754,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C27">
-        <v>32</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
@@ -769,11 +769,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C28">
-        <v>58</v>
+        <v>720</v>
       </c>
     </row>
     <row r="29">
@@ -784,11 +784,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C29">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -799,11 +799,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C30">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -814,11 +814,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C31">
-        <v>160</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
@@ -829,11 +829,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C32">
-        <v>759</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -844,11 +844,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C33">
-        <v>72</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34">
@@ -859,11 +859,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
@@ -874,11 +874,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -889,11 +889,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C36">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -904,11 +904,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C37">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -919,11 +919,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C38">
-        <v>147</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39">
@@ -934,11 +934,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C39">
-        <v>370</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -949,11 +949,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C40">
-        <v>52</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41">
@@ -964,11 +964,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C41">
-        <v>295</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42">
@@ -979,11 +979,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C42">
-        <v>508</v>
+      <c r="C44">
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,56 +379,56 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C2">
-        <v>68</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C3">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6">
@@ -439,11 +439,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C6">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -454,11 +454,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -469,146 +469,146 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C9">
-        <v>420</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C10">
-        <v>27</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C11">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C12">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C13">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C14">
-        <v>76</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -619,7 +619,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C18">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C19">
-        <v>36</v>
+        <v>720</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C20">
-        <v>74</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C21">
-        <v>126</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C23">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C24">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C25">
-        <v>216</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -739,11 +739,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C26">
-        <v>73</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
@@ -754,11 +754,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C27">
-        <v>180</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28">
@@ -769,11 +769,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C28">
-        <v>720</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -784,11 +784,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C29">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
@@ -799,11 +799,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C30">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -814,11 +814,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C31">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
@@ -829,11 +829,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C32">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -844,176 +844,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C33">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>NBH</t>
-        </is>
-      </c>
-      <c r="C34">
         <v>36</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>QNI</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>QTI</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>TNH</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>TNN</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>TQG</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>TTH</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,46 +374,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C2">
-        <v>143</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C3">
-        <v>78</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -424,11 +424,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C5">
-        <v>360</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -439,11 +439,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C6">
-        <v>72</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
@@ -454,41 +454,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C8">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C10">
-        <v>223</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C11">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C12">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C13">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14">
@@ -559,11 +559,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C14">
-        <v>33</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -574,11 +574,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C15">
-        <v>34</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="16">
@@ -589,11 +589,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C16">
-        <v>144</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -604,11 +604,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C17">
-        <v>73</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C18">
-        <v>180</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C19">
-        <v>720</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>202</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
@@ -679,11 +679,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C22">
-        <v>306</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="C23">
-        <v>46</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C25">
-        <v>15</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26">
@@ -739,11 +739,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C26">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
@@ -754,11 +754,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C27">
-        <v>211</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="28">
@@ -769,11 +769,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="29">
@@ -784,11 +784,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C29">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30">
@@ -799,11 +799,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C30">
-        <v>20</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
@@ -814,11 +814,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C31">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
@@ -829,11 +829,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33">
@@ -844,11 +844,56 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C33">
-        <v>36</v>
+      <c r="C36">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/ton_di_duong_bc.xlsx
+++ b/data/ton_di_duong_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,41 +379,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C2">
-        <v>45</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C3">
-        <v>116</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -424,41 +424,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C5">
-        <v>72</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C6">
-        <v>180</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C7">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -469,11 +469,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C8">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -484,11 +484,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C9">
-        <v>46</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
@@ -499,11 +499,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C10">
-        <v>180</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -514,11 +514,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -529,11 +529,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C12">
-        <v>16</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -544,11 +544,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C13">
-        <v>105</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14">
@@ -559,11 +559,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C14">
-        <v>180</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15">
@@ -574,11 +574,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C15">
-        <v>2232</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -589,11 +589,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17">
@@ -604,11 +604,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C17">
-        <v>324</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18">
@@ -619,11 +619,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C18">
-        <v>1440</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19">
@@ -634,11 +634,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C19">
-        <v>96</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20">
@@ -649,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C20">
-        <v>108</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21">
@@ -664,11 +664,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C21">
-        <v>180</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>396</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -694,11 +694,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C23">
-        <v>180</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24">
@@ -709,11 +709,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -724,11 +724,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C25">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26">
@@ -739,11 +739,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C26">
-        <v>54</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27">
@@ -754,11 +754,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C27">
-        <v>1182</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
@@ -769,11 +769,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C28">
-        <v>2164</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29">
@@ -784,11 +784,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C29">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
@@ -799,11 +799,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C30">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
@@ -814,11 +814,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C31">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
@@ -829,11 +829,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C32">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
@@ -844,11 +844,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C33">
-        <v>30</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34">
@@ -859,41 +859,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>TTH</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>10</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
